--- a/jogos_2026-06-02.xlsx
+++ b/jogos_2026-06-02.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-06-02.xlsx
+++ b/jogos_2026-06-02.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.69</v>
+        <v>4.02</v>
       </c>
       <c r="O2" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.72</v>
+        <v>5.56</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="S2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="U2" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-06-02.xlsx
+++ b/jogos_2026-06-02.xlsx
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.02</v>
+        <v>5.97</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.56</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S2" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="T2" t="n">
         <v>2.31</v>
@@ -755,34 +755,34 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" t="n">
         <v>2.49</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AB2" t="n">
         <v>1.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.4</v>
+        <v>4.65</v>
       </c>
       <c r="AD2" t="n">
         <v>1.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-06-02.xlsx
+++ b/jogos_2026-06-02.xlsx
@@ -702,16 +702,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -786,12 +786,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46175.66666666666</v>
